--- a/src/LARS/processed_data_with_neighborhood.xlsx
+++ b/src/LARS/processed_data_with_neighborhood.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y339"/>
+  <dimension ref="A1:AA341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,6 +558,16 @@
           <t>neighborhood_english</t>
         </is>
       </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>violation_numeric</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -659,6 +669,8 @@
           <t>Al Mowata</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -760,6 +772,8 @@
           <t>An Nasariyah</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -861,6 +875,8 @@
           <t>Al Qaa Al Barid</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -962,6 +978,8 @@
           <t>Al Wasita</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1063,6 +1081,8 @@
           <t>An Nasariyah</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1164,6 +1184,8 @@
           <t>Al Rashid</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1265,6 +1287,8 @@
           <t>As Salmiyah</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1366,6 +1390,8 @@
           <t>As Salmiyah</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1467,6 +1493,8 @@
           <t>Al Bishr</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1568,6 +1596,8 @@
           <t>An Nasariyah</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1669,6 +1699,8 @@
           <t>At Takhassusi</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1770,6 +1802,8 @@
           <t>Al Bishr</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1871,6 +1905,8 @@
           <t>Al Fayziyyah</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1972,6 +2008,8 @@
           <t>Al Hedaya</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2073,6 +2111,8 @@
           <t>At Taghirah</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2174,6 +2214,8 @@
           <t>Wahtan</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2275,6 +2317,8 @@
           <t>Al Labidiyah</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2376,6 +2420,8 @@
           <t>Al Bishr</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2477,6 +2523,8 @@
           <t>Al Akhdar</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2578,6 +2626,8 @@
           <t>An Naqib</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2679,6 +2729,8 @@
           <t>Al Ufuq</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2780,6 +2832,8 @@
           <t>At Taghirah</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2881,6 +2935,8 @@
           <t>Al Iskan</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2982,6 +3038,8 @@
           <t>An Naqib</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3083,6 +3141,8 @@
           <t>Al Qaa Al Barid</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3184,6 +3244,8 @@
           <t>Ash Shamas</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3285,6 +3347,8 @@
           <t>Al Mowata</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3386,6 +3450,8 @@
           <t>As Safra</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3487,6 +3553,8 @@
           <t>As Salam</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3588,6 +3656,8 @@
           <t>Al Jamioyin</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3689,6 +3759,8 @@
           <t>Al Rashid</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3790,6 +3862,8 @@
           <t>Al Jamioyin</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3891,6 +3965,8 @@
           <t>Al Akhdar</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3992,6 +4068,8 @@
           <t>Ar Rafiah</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4093,6 +4171,8 @@
           <t>Al Rashid</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4194,6 +4274,8 @@
           <t>Al Maared</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4295,6 +4377,8 @@
           <t>At Takhassusi</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4396,6 +4480,8 @@
           <t>Al Akhdar</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4497,6 +4583,8 @@
           <t>Al Amn</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4598,6 +4686,8 @@
           <t>As Sadah</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4699,6 +4789,8 @@
           <t>Al Maared</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4800,6 +4892,8 @@
           <t>Al Bishr</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4901,6 +4995,8 @@
           <t>Al Amn</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5002,6 +5098,8 @@
           <t>Al Maared</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5103,6 +5201,8 @@
           <t>At Takhassusi</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5204,6 +5304,8 @@
           <t>Mishal</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5305,6 +5407,8 @@
           <t>As Sabihah</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5406,6 +5510,8 @@
           <t>Al Iskan</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5507,6 +5613,8 @@
           <t>Ain Adh Dhib</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5608,6 +5716,8 @@
           <t>An Nahdah</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5709,6 +5819,8 @@
           <t>Mishal</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5810,6 +5922,8 @@
           <t>Ash Shamas</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5911,6 +6025,8 @@
           <t>Al Hedaya</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -6012,6 +6128,8 @@
           <t>As Salam</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6113,6 +6231,8 @@
           <t>Al Iskan</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6214,6 +6334,8 @@
           <t>Al Khalidiyah</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -6315,6 +6437,8 @@
           <t>As Safra</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6416,6 +6540,8 @@
           <t>Al Mowata</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6517,6 +6643,8 @@
           <t>An Naziyah</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6618,6 +6746,8 @@
           <t>Al Hedaya</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6719,6 +6849,8 @@
           <t>Al Bishr</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6820,6 +6952,8 @@
           <t>Wahtan</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr"/>
+      <c r="AA63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6921,6 +7055,8 @@
           <t>Al Buraykah</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr"/>
+      <c r="AA64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -7022,6 +7158,8 @@
           <t>Ar Rafiah</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr"/>
+      <c r="AA65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -7123,6 +7261,8 @@
           <t>As Sadah</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr"/>
+      <c r="AA66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -7224,6 +7364,8 @@
           <t>Al Ufuq</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr"/>
+      <c r="AA67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -7325,6 +7467,8 @@
           <t>Mishal</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr"/>
+      <c r="AA68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -7426,6 +7570,8 @@
           <t>Ghannamah</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr"/>
+      <c r="AA69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -7527,6 +7673,8 @@
           <t>Al Iskan</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr"/>
+      <c r="AA70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -7628,6 +7776,8 @@
           <t>Al Fayziyyah</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr"/>
+      <c r="AA71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -7729,6 +7879,8 @@
           <t>Al Jamioyin</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr"/>
+      <c r="AA72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -7830,6 +7982,8 @@
           <t>Al Labidiyah</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr"/>
+      <c r="AA73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -7931,6 +8085,8 @@
           <t>An Nassar</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr"/>
+      <c r="AA74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -8032,6 +8188,8 @@
           <t>Al Maared</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr"/>
+      <c r="AA75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -8133,6 +8291,8 @@
           <t>An Nassar</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr"/>
+      <c r="AA76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -8234,6 +8394,8 @@
           <t>Al Muntazah</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr"/>
+      <c r="AA77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -8335,6 +8497,8 @@
           <t>Al Ulya</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr"/>
+      <c r="AA78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -8436,6 +8600,8 @@
           <t>Al Labidiyah</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr"/>
+      <c r="AA79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -8537,6 +8703,8 @@
           <t>At Taghirah</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr"/>
+      <c r="AA80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -8638,6 +8806,8 @@
           <t>Al Fakhriyah</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr"/>
+      <c r="AA81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -8739,6 +8909,8 @@
           <t>An Nasariyah</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr"/>
+      <c r="AA82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -8840,6 +9012,8 @@
           <t>Ar Rafiah</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr"/>
+      <c r="AA83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -8941,6 +9115,8 @@
           <t>Al Maared</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr"/>
+      <c r="AA84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -9042,6 +9218,8 @@
           <t>An Naziyah</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr"/>
+      <c r="AA85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -9143,6 +9321,8 @@
           <t>Al Fayziyyah</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr"/>
+      <c r="AA86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -9244,6 +9424,8 @@
           <t>Ash Shamas</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr"/>
+      <c r="AA87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -9345,6 +9527,8 @@
           <t>Ash Shamas</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr"/>
+      <c r="AA88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -9446,6 +9630,8 @@
           <t>Al Rashid</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr"/>
+      <c r="AA89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -9547,6 +9733,8 @@
           <t>As Sabihah</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr"/>
+      <c r="AA90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -9648,6 +9836,8 @@
           <t>An Naqa Ash Sharqi</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr"/>
+      <c r="AA91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -9749,6 +9939,8 @@
           <t>Al Buraykah</t>
         </is>
       </c>
+      <c r="Z92" t="inlineStr"/>
+      <c r="AA92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -9850,6 +10042,8 @@
           <t>Al Qaa Al Barid</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr"/>
+      <c r="AA93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -9951,6 +10145,8 @@
           <t>Al Ajibah</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr"/>
+      <c r="AA94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -10052,6 +10248,8 @@
           <t>An Nahdah</t>
         </is>
       </c>
+      <c r="Z95" t="inlineStr"/>
+      <c r="AA95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -10153,6 +10351,8 @@
           <t>An Nasariyah</t>
         </is>
       </c>
+      <c r="Z96" t="inlineStr"/>
+      <c r="AA96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -10254,6 +10454,8 @@
           <t>Al Jamioyin</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr"/>
+      <c r="AA97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -10355,6 +10557,8 @@
           <t>Al Wasita</t>
         </is>
       </c>
+      <c r="Z98" t="inlineStr"/>
+      <c r="AA98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -10456,6 +10660,8 @@
           <t>Al Fayziyyah</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr"/>
+      <c r="AA99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -10557,6 +10763,8 @@
           <t>An Naqa Ash Sharqi</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr"/>
+      <c r="AA100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -10658,6 +10866,8 @@
           <t>Al Muntazah</t>
         </is>
       </c>
+      <c r="Z101" t="inlineStr"/>
+      <c r="AA101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -10759,6 +10969,8 @@
           <t>Al Amn</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr"/>
+      <c r="AA102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -10860,6 +11072,8 @@
           <t>Mishal</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr"/>
+      <c r="AA103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -10961,6 +11175,8 @@
           <t>Al Qaa Al Barid</t>
         </is>
       </c>
+      <c r="Z104" t="inlineStr"/>
+      <c r="AA104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -11062,6 +11278,8 @@
           <t>Wahtan</t>
         </is>
       </c>
+      <c r="Z105" t="inlineStr"/>
+      <c r="AA105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -11163,6 +11381,8 @@
           <t>As Safra</t>
         </is>
       </c>
+      <c r="Z106" t="inlineStr"/>
+      <c r="AA106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -11264,6 +11484,8 @@
           <t>Al Amn</t>
         </is>
       </c>
+      <c r="Z107" t="inlineStr"/>
+      <c r="AA107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -11365,6 +11587,8 @@
           <t>Al Fayziyyah</t>
         </is>
       </c>
+      <c r="Z108" t="inlineStr"/>
+      <c r="AA108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -11466,6 +11690,8 @@
           <t>Al Hedaya</t>
         </is>
       </c>
+      <c r="Z109" t="inlineStr"/>
+      <c r="AA109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -11567,6 +11793,8 @@
           <t>Al Ulya</t>
         </is>
       </c>
+      <c r="Z110" t="inlineStr"/>
+      <c r="AA110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -11668,6 +11896,8 @@
           <t>Qurtubah</t>
         </is>
       </c>
+      <c r="Z111" t="inlineStr"/>
+      <c r="AA111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -11769,6 +11999,8 @@
           <t>Al Maared</t>
         </is>
       </c>
+      <c r="Z112" t="inlineStr"/>
+      <c r="AA112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -11870,6 +12102,8 @@
           <t>As Sadah</t>
         </is>
       </c>
+      <c r="Z113" t="inlineStr"/>
+      <c r="AA113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -11971,6 +12205,8 @@
           <t>Ain Adh Dhib</t>
         </is>
       </c>
+      <c r="Z114" t="inlineStr"/>
+      <c r="AA114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -12072,6 +12308,8 @@
           <t>Al Iskan</t>
         </is>
       </c>
+      <c r="Z115" t="inlineStr"/>
+      <c r="AA115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -12173,6 +12411,8 @@
           <t>Al Awazim</t>
         </is>
       </c>
+      <c r="Z116" t="inlineStr"/>
+      <c r="AA116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -12274,6 +12514,8 @@
           <t>As Salam</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr"/>
+      <c r="AA117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -12375,6 +12617,8 @@
           <t>Jameana</t>
         </is>
       </c>
+      <c r="Z118" t="inlineStr"/>
+      <c r="AA118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -12476,6 +12720,8 @@
           <t>Al Fakhriyah</t>
         </is>
       </c>
+      <c r="Z119" t="inlineStr"/>
+      <c r="AA119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -12577,6 +12823,8 @@
           <t>Jameana</t>
         </is>
       </c>
+      <c r="Z120" t="inlineStr"/>
+      <c r="AA120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -12678,6 +12926,8 @@
           <t>Al Buraykah</t>
         </is>
       </c>
+      <c r="Z121" t="inlineStr"/>
+      <c r="AA121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -12779,6 +13029,8 @@
           <t>Al Bishr</t>
         </is>
       </c>
+      <c r="Z122" t="inlineStr"/>
+      <c r="AA122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -12880,6 +13132,8 @@
           <t>Al Wasita</t>
         </is>
       </c>
+      <c r="Z123" t="inlineStr"/>
+      <c r="AA123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -12981,6 +13235,8 @@
           <t>Al Buraykah</t>
         </is>
       </c>
+      <c r="Z124" t="inlineStr"/>
+      <c r="AA124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -13082,6 +13338,8 @@
           <t>As Salmiyah</t>
         </is>
       </c>
+      <c r="Z125" t="inlineStr"/>
+      <c r="AA125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -13183,6 +13441,8 @@
           <t>Al Fakhriyah</t>
         </is>
       </c>
+      <c r="Z126" t="inlineStr"/>
+      <c r="AA126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -13284,6 +13544,8 @@
           <t>An Naziyah</t>
         </is>
       </c>
+      <c r="Z127" t="inlineStr"/>
+      <c r="AA127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -13385,6 +13647,8 @@
           <t>Al Muntazah</t>
         </is>
       </c>
+      <c r="Z128" t="inlineStr"/>
+      <c r="AA128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -13486,6 +13750,8 @@
           <t>As Salmiyah</t>
         </is>
       </c>
+      <c r="Z129" t="inlineStr"/>
+      <c r="AA129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -13587,6 +13853,8 @@
           <t>Al Ufuq</t>
         </is>
       </c>
+      <c r="Z130" t="inlineStr"/>
+      <c r="AA130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -13688,6 +13956,8 @@
           <t>Al Ulya</t>
         </is>
       </c>
+      <c r="Z131" t="inlineStr"/>
+      <c r="AA131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -13789,6 +14059,8 @@
           <t>Qurtubah</t>
         </is>
       </c>
+      <c r="Z132" t="inlineStr"/>
+      <c r="AA132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -13890,6 +14162,8 @@
           <t>An Naziyah</t>
         </is>
       </c>
+      <c r="Z133" t="inlineStr"/>
+      <c r="AA133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -13991,6 +14265,8 @@
           <t>Al Jamioyin</t>
         </is>
       </c>
+      <c r="Z134" t="inlineStr"/>
+      <c r="AA134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -14092,6 +14368,8 @@
           <t>Al Bishr</t>
         </is>
       </c>
+      <c r="Z135" t="inlineStr"/>
+      <c r="AA135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -14193,6 +14471,8 @@
           <t>Jameana</t>
         </is>
       </c>
+      <c r="Z136" t="inlineStr"/>
+      <c r="AA136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -14294,6 +14574,8 @@
           <t>Qurtubah</t>
         </is>
       </c>
+      <c r="Z137" t="inlineStr"/>
+      <c r="AA137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -14395,6 +14677,8 @@
           <t>Wahtan</t>
         </is>
       </c>
+      <c r="Z138" t="inlineStr"/>
+      <c r="AA138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -14496,6 +14780,8 @@
           <t>An Nasariyah</t>
         </is>
       </c>
+      <c r="Z139" t="inlineStr"/>
+      <c r="AA139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -14597,6 +14883,8 @@
           <t>Al Akhdar</t>
         </is>
       </c>
+      <c r="Z140" t="inlineStr"/>
+      <c r="AA140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -14698,6 +14986,8 @@
           <t>An Nasariyah</t>
         </is>
       </c>
+      <c r="Z141" t="inlineStr"/>
+      <c r="AA141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -14799,6 +15089,8 @@
           <t>An Naqa Ash Sharqi</t>
         </is>
       </c>
+      <c r="Z142" t="inlineStr"/>
+      <c r="AA142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -14900,6 +15192,8 @@
           <t>As Safra</t>
         </is>
       </c>
+      <c r="Z143" t="inlineStr"/>
+      <c r="AA143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -15001,6 +15295,8 @@
           <t>As Sabihah</t>
         </is>
       </c>
+      <c r="Z144" t="inlineStr"/>
+      <c r="AA144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -15102,6 +15398,8 @@
           <t>Mishal</t>
         </is>
       </c>
+      <c r="Z145" t="inlineStr"/>
+      <c r="AA145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -15203,6 +15501,8 @@
           <t>As Salam</t>
         </is>
       </c>
+      <c r="Z146" t="inlineStr"/>
+      <c r="AA146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -15304,6 +15604,8 @@
           <t>Az Zirai</t>
         </is>
       </c>
+      <c r="Z147" t="inlineStr"/>
+      <c r="AA147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -15405,6 +15707,8 @@
           <t>At Takhassusi</t>
         </is>
       </c>
+      <c r="Z148" t="inlineStr"/>
+      <c r="AA148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -15506,6 +15810,8 @@
           <t>Al Iskan</t>
         </is>
       </c>
+      <c r="Z149" t="inlineStr"/>
+      <c r="AA149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -15607,6 +15913,8 @@
           <t>Al Qaa Al Barid</t>
         </is>
       </c>
+      <c r="Z150" t="inlineStr"/>
+      <c r="AA150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -15708,6 +16016,8 @@
           <t>Al Fayziyyah</t>
         </is>
       </c>
+      <c r="Z151" t="inlineStr"/>
+      <c r="AA151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -15809,6 +16119,8 @@
           <t>An Naziyah</t>
         </is>
       </c>
+      <c r="Z152" t="inlineStr"/>
+      <c r="AA152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -15910,6 +16222,8 @@
           <t>Al Maared</t>
         </is>
       </c>
+      <c r="Z153" t="inlineStr"/>
+      <c r="AA153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -16011,6 +16325,8 @@
           <t>Al Rashid</t>
         </is>
       </c>
+      <c r="Z154" t="inlineStr"/>
+      <c r="AA154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -16112,6 +16428,8 @@
           <t>Al Mowata</t>
         </is>
       </c>
+      <c r="Z155" t="inlineStr"/>
+      <c r="AA155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -16213,6 +16531,8 @@
           <t>Mishal</t>
         </is>
       </c>
+      <c r="Z156" t="inlineStr"/>
+      <c r="AA156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -16314,6 +16634,8 @@
           <t>Al Fayziyyah</t>
         </is>
       </c>
+      <c r="Z157" t="inlineStr"/>
+      <c r="AA157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -16415,6 +16737,8 @@
           <t>Ibn Subayh</t>
         </is>
       </c>
+      <c r="Z158" t="inlineStr"/>
+      <c r="AA158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -16516,6 +16840,8 @@
           <t>Al Hedaya</t>
         </is>
       </c>
+      <c r="Z159" t="inlineStr"/>
+      <c r="AA159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -16617,6 +16943,8 @@
           <t>Al Akhdar</t>
         </is>
       </c>
+      <c r="Z160" t="inlineStr"/>
+      <c r="AA160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -16718,6 +17046,8 @@
           <t>As Safra</t>
         </is>
       </c>
+      <c r="Z161" t="inlineStr"/>
+      <c r="AA161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -16819,6 +17149,8 @@
           <t>Al Ulya</t>
         </is>
       </c>
+      <c r="Z162" t="inlineStr"/>
+      <c r="AA162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -16920,6 +17252,8 @@
           <t>At Taghirah</t>
         </is>
       </c>
+      <c r="Z163" t="inlineStr"/>
+      <c r="AA163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -17021,6 +17355,8 @@
           <t>Al Iskan</t>
         </is>
       </c>
+      <c r="Z164" t="inlineStr"/>
+      <c r="AA164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -17122,6 +17458,8 @@
           <t>Ibn Subayh</t>
         </is>
       </c>
+      <c r="Z165" t="inlineStr"/>
+      <c r="AA165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -17223,6 +17561,8 @@
           <t>Al Ulya</t>
         </is>
       </c>
+      <c r="Z166" t="inlineStr"/>
+      <c r="AA166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -17324,6 +17664,8 @@
           <t>Al Khalidiyah</t>
         </is>
       </c>
+      <c r="Z167" t="inlineStr"/>
+      <c r="AA167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -17425,6 +17767,8 @@
           <t>Ghannamah</t>
         </is>
       </c>
+      <c r="Z168" t="inlineStr"/>
+      <c r="AA168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -17526,6 +17870,8 @@
           <t>At Takhassusi</t>
         </is>
       </c>
+      <c r="Z169" t="inlineStr"/>
+      <c r="AA169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -17627,6 +17973,8 @@
           <t>Al Bishr</t>
         </is>
       </c>
+      <c r="Z170" t="inlineStr"/>
+      <c r="AA170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -17728,6 +18076,8 @@
           <t>Al Fakhriyah</t>
         </is>
       </c>
+      <c r="Z171" t="inlineStr"/>
+      <c r="AA171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -17829,6 +18179,8 @@
           <t>Ain Adh Dhib</t>
         </is>
       </c>
+      <c r="Z172" t="inlineStr"/>
+      <c r="AA172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -17930,6 +18282,8 @@
           <t>Ain Adh Dhib</t>
         </is>
       </c>
+      <c r="Z173" t="inlineStr"/>
+      <c r="AA173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -18031,6 +18385,8 @@
           <t>Al Maared</t>
         </is>
       </c>
+      <c r="Z174" t="inlineStr"/>
+      <c r="AA174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -18132,6 +18488,8 @@
           <t>Ibn Subayh</t>
         </is>
       </c>
+      <c r="Z175" t="inlineStr"/>
+      <c r="AA175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -18233,6 +18591,8 @@
           <t>Al Mowata</t>
         </is>
       </c>
+      <c r="Z176" t="inlineStr"/>
+      <c r="AA176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -18334,6 +18694,8 @@
           <t>Al Awazim</t>
         </is>
       </c>
+      <c r="Z177" t="inlineStr"/>
+      <c r="AA177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -18435,6 +18797,8 @@
           <t>As Salmiyah</t>
         </is>
       </c>
+      <c r="Z178" t="inlineStr"/>
+      <c r="AA178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -18536,6 +18900,8 @@
           <t>Ash Shamas</t>
         </is>
       </c>
+      <c r="Z179" t="inlineStr"/>
+      <c r="AA179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -18637,6 +19003,8 @@
           <t>Al Labidiyah</t>
         </is>
       </c>
+      <c r="Z180" t="inlineStr"/>
+      <c r="AA180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -18738,6 +19106,8 @@
           <t>An Naqib</t>
         </is>
       </c>
+      <c r="Z181" t="inlineStr"/>
+      <c r="AA181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -18839,6 +19209,8 @@
           <t>Al Qaa Al Barid</t>
         </is>
       </c>
+      <c r="Z182" t="inlineStr"/>
+      <c r="AA182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -18940,6 +19312,8 @@
           <t>Al Ajibah</t>
         </is>
       </c>
+      <c r="Z183" t="inlineStr"/>
+      <c r="AA183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -19041,6 +19415,8 @@
           <t>Al Labidiyah</t>
         </is>
       </c>
+      <c r="Z184" t="inlineStr"/>
+      <c r="AA184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -19142,6 +19518,8 @@
           <t>An Nahdah</t>
         </is>
       </c>
+      <c r="Z185" t="inlineStr"/>
+      <c r="AA185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -19243,6 +19621,8 @@
           <t>As Sadah</t>
         </is>
       </c>
+      <c r="Z186" t="inlineStr"/>
+      <c r="AA186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -19344,6 +19724,8 @@
           <t>Al Mowata</t>
         </is>
       </c>
+      <c r="Z187" t="inlineStr"/>
+      <c r="AA187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -19445,6 +19827,8 @@
           <t>Ghannamah</t>
         </is>
       </c>
+      <c r="Z188" t="inlineStr"/>
+      <c r="AA188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -19546,6 +19930,8 @@
           <t>Az Zirai</t>
         </is>
       </c>
+      <c r="Z189" t="inlineStr"/>
+      <c r="AA189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -19647,6 +20033,8 @@
           <t>Ad Dahi</t>
         </is>
       </c>
+      <c r="Z190" t="inlineStr"/>
+      <c r="AA190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -19748,6 +20136,8 @@
           <t>As Salam</t>
         </is>
       </c>
+      <c r="Z191" t="inlineStr"/>
+      <c r="AA191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -19849,6 +20239,8 @@
           <t>Al Hedaya</t>
         </is>
       </c>
+      <c r="Z192" t="inlineStr"/>
+      <c r="AA192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -19950,6 +20342,8 @@
           <t>Al Fakhriyah</t>
         </is>
       </c>
+      <c r="Z193" t="inlineStr"/>
+      <c r="AA193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -20051,6 +20445,8 @@
           <t>Al Iskan</t>
         </is>
       </c>
+      <c r="Z194" t="inlineStr"/>
+      <c r="AA194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -20152,6 +20548,8 @@
           <t>Al Maared</t>
         </is>
       </c>
+      <c r="Z195" t="inlineStr"/>
+      <c r="AA195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -20253,6 +20651,8 @@
           <t>Al Iskan</t>
         </is>
       </c>
+      <c r="Z196" t="inlineStr"/>
+      <c r="AA196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -20354,6 +20754,8 @@
           <t>Al Iskan</t>
         </is>
       </c>
+      <c r="Z197" t="inlineStr"/>
+      <c r="AA197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -20455,6 +20857,8 @@
           <t>An Naqa Ash Sharqi</t>
         </is>
       </c>
+      <c r="Z198" t="inlineStr"/>
+      <c r="AA198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -20556,6 +20960,8 @@
           <t>Ash Shamas</t>
         </is>
       </c>
+      <c r="Z199" t="inlineStr"/>
+      <c r="AA199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -20657,6 +21063,8 @@
           <t>Ibn Subayh</t>
         </is>
       </c>
+      <c r="Z200" t="inlineStr"/>
+      <c r="AA200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -20758,6 +21166,8 @@
           <t>Al Amn</t>
         </is>
       </c>
+      <c r="Z201" t="inlineStr"/>
+      <c r="AA201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -20859,6 +21269,8 @@
           <t>An Nahdah</t>
         </is>
       </c>
+      <c r="Z202" t="inlineStr"/>
+      <c r="AA202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -20960,6 +21372,8 @@
           <t>Al Wasita</t>
         </is>
       </c>
+      <c r="Z203" t="inlineStr"/>
+      <c r="AA203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -21061,6 +21475,8 @@
           <t>Al Jamioyin</t>
         </is>
       </c>
+      <c r="Z204" t="inlineStr"/>
+      <c r="AA204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -21162,6 +21578,8 @@
           <t>Al Maared</t>
         </is>
       </c>
+      <c r="Z205" t="inlineStr"/>
+      <c r="AA205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -21263,6 +21681,8 @@
           <t>Al Jamioyin</t>
         </is>
       </c>
+      <c r="Z206" t="inlineStr"/>
+      <c r="AA206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -21364,6 +21784,8 @@
           <t>Al Jamioyin</t>
         </is>
       </c>
+      <c r="Z207" t="inlineStr"/>
+      <c r="AA207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -21465,6 +21887,8 @@
           <t>An Naziyah</t>
         </is>
       </c>
+      <c r="Z208" t="inlineStr"/>
+      <c r="AA208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -21566,6 +21990,8 @@
           <t>Al Amn</t>
         </is>
       </c>
+      <c r="Z209" t="inlineStr"/>
+      <c r="AA209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -21667,6 +22093,8 @@
           <t>As Sadah</t>
         </is>
       </c>
+      <c r="Z210" t="inlineStr"/>
+      <c r="AA210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -21768,6 +22196,8 @@
           <t>An Naziyah</t>
         </is>
       </c>
+      <c r="Z211" t="inlineStr"/>
+      <c r="AA211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -21869,6 +22299,8 @@
           <t>Al Ufuq</t>
         </is>
       </c>
+      <c r="Z212" t="inlineStr"/>
+      <c r="AA212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -21970,6 +22402,8 @@
           <t>Al Mowata</t>
         </is>
       </c>
+      <c r="Z213" t="inlineStr"/>
+      <c r="AA213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -22071,6 +22505,8 @@
           <t>Ibn Subayh</t>
         </is>
       </c>
+      <c r="Z214" t="inlineStr"/>
+      <c r="AA214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -22172,6 +22608,8 @@
           <t>Al Ufuq</t>
         </is>
       </c>
+      <c r="Z215" t="inlineStr"/>
+      <c r="AA215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -22273,6 +22711,8 @@
           <t>Al Hedaya</t>
         </is>
       </c>
+      <c r="Z216" t="inlineStr"/>
+      <c r="AA216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -22374,6 +22814,8 @@
           <t>Al Labidiyah</t>
         </is>
       </c>
+      <c r="Z217" t="inlineStr"/>
+      <c r="AA217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -22475,6 +22917,8 @@
           <t>Ad Dahi</t>
         </is>
       </c>
+      <c r="Z218" t="inlineStr"/>
+      <c r="AA218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -22576,6 +23020,8 @@
           <t>Ghannamah</t>
         </is>
       </c>
+      <c r="Z219" t="inlineStr"/>
+      <c r="AA219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -22677,6 +23123,8 @@
           <t>Al Iskan</t>
         </is>
       </c>
+      <c r="Z220" t="inlineStr"/>
+      <c r="AA220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -22778,6 +23226,8 @@
           <t>As Salmiyah</t>
         </is>
       </c>
+      <c r="Z221" t="inlineStr"/>
+      <c r="AA221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -22879,6 +23329,8 @@
           <t>Ibn Subayh</t>
         </is>
       </c>
+      <c r="Z222" t="inlineStr"/>
+      <c r="AA222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -22980,6 +23432,8 @@
           <t>Ar Rafiah</t>
         </is>
       </c>
+      <c r="Z223" t="inlineStr"/>
+      <c r="AA223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -23081,6 +23535,8 @@
           <t>As Salam</t>
         </is>
       </c>
+      <c r="Z224" t="inlineStr"/>
+      <c r="AA224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -23182,6 +23638,8 @@
           <t>Al Wasita</t>
         </is>
       </c>
+      <c r="Z225" t="inlineStr"/>
+      <c r="AA225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -23283,6 +23741,8 @@
           <t>An Nahdah</t>
         </is>
       </c>
+      <c r="Z226" t="inlineStr"/>
+      <c r="AA226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -23384,6 +23844,8 @@
           <t>Al Fakhriyah</t>
         </is>
       </c>
+      <c r="Z227" t="inlineStr"/>
+      <c r="AA227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -23485,6 +23947,8 @@
           <t>Ain Adh Dhib</t>
         </is>
       </c>
+      <c r="Z228" t="inlineStr"/>
+      <c r="AA228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -23586,6 +24050,8 @@
           <t>An Naqa Ash Sharqi</t>
         </is>
       </c>
+      <c r="Z229" t="inlineStr"/>
+      <c r="AA229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -23687,6 +24153,8 @@
           <t>At Takhassusi</t>
         </is>
       </c>
+      <c r="Z230" t="inlineStr"/>
+      <c r="AA230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -23788,6 +24256,8 @@
           <t>Ar Rafiah</t>
         </is>
       </c>
+      <c r="Z231" t="inlineStr"/>
+      <c r="AA231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -23889,6 +24359,8 @@
           <t>An Nassar</t>
         </is>
       </c>
+      <c r="Z232" t="inlineStr"/>
+      <c r="AA232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -23990,6 +24462,8 @@
           <t>Al Ajibah</t>
         </is>
       </c>
+      <c r="Z233" t="inlineStr"/>
+      <c r="AA233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -24091,6 +24565,8 @@
           <t>Al Fayziyyah</t>
         </is>
       </c>
+      <c r="Z234" t="inlineStr"/>
+      <c r="AA234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -24192,6 +24668,8 @@
           <t>At Takhassusi</t>
         </is>
       </c>
+      <c r="Z235" t="inlineStr"/>
+      <c r="AA235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -24293,6 +24771,8 @@
           <t>Al Bishr</t>
         </is>
       </c>
+      <c r="Z236" t="inlineStr"/>
+      <c r="AA236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -24394,6 +24874,8 @@
           <t>Al Iskan</t>
         </is>
       </c>
+      <c r="Z237" t="inlineStr"/>
+      <c r="AA237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -24495,6 +24977,8 @@
           <t>Al Iskan</t>
         </is>
       </c>
+      <c r="Z238" t="inlineStr"/>
+      <c r="AA238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -24596,6 +25080,8 @@
           <t>Al Mowata</t>
         </is>
       </c>
+      <c r="Z239" t="inlineStr"/>
+      <c r="AA239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -24697,6 +25183,8 @@
           <t>Al Buraykah</t>
         </is>
       </c>
+      <c r="Z240" t="inlineStr"/>
+      <c r="AA240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -24798,6 +25286,8 @@
           <t>Ad Dahi</t>
         </is>
       </c>
+      <c r="Z241" t="inlineStr"/>
+      <c r="AA241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -24899,6 +25389,8 @@
           <t>At Taghirah</t>
         </is>
       </c>
+      <c r="Z242" t="inlineStr"/>
+      <c r="AA242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -25000,6 +25492,8 @@
           <t>At Takhassusi</t>
         </is>
       </c>
+      <c r="Z243" t="inlineStr"/>
+      <c r="AA243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -25101,6 +25595,8 @@
           <t>Ibn Subayh</t>
         </is>
       </c>
+      <c r="Z244" t="inlineStr"/>
+      <c r="AA244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -25202,6 +25698,8 @@
           <t>Ain Adh Dhib</t>
         </is>
       </c>
+      <c r="Z245" t="inlineStr"/>
+      <c r="AA245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -25303,6 +25801,8 @@
           <t>Al Awazim</t>
         </is>
       </c>
+      <c r="Z246" t="inlineStr"/>
+      <c r="AA246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -25404,6 +25904,8 @@
           <t>At Taghirah</t>
         </is>
       </c>
+      <c r="Z247" t="inlineStr"/>
+      <c r="AA247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -25505,6 +26007,8 @@
           <t>An Nassar</t>
         </is>
       </c>
+      <c r="Z248" t="inlineStr"/>
+      <c r="AA248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -25606,6 +26110,8 @@
           <t>Al Khalidiyah</t>
         </is>
       </c>
+      <c r="Z249" t="inlineStr"/>
+      <c r="AA249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -25707,6 +26213,8 @@
           <t>Al Hedaya</t>
         </is>
       </c>
+      <c r="Z250" t="inlineStr"/>
+      <c r="AA250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -25808,6 +26316,8 @@
           <t>As Sadah</t>
         </is>
       </c>
+      <c r="Z251" t="inlineStr"/>
+      <c r="AA251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -25909,6 +26419,8 @@
           <t>Az Zirai</t>
         </is>
       </c>
+      <c r="Z252" t="inlineStr"/>
+      <c r="AA252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -26010,6 +26522,8 @@
           <t>Al Iskan</t>
         </is>
       </c>
+      <c r="Z253" t="inlineStr"/>
+      <c r="AA253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -26111,6 +26625,8 @@
           <t>Al Ulya</t>
         </is>
       </c>
+      <c r="Z254" t="inlineStr"/>
+      <c r="AA254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -26212,6 +26728,8 @@
           <t>As Sadah</t>
         </is>
       </c>
+      <c r="Z255" t="inlineStr"/>
+      <c r="AA255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -26313,6 +26831,8 @@
           <t>As Salam</t>
         </is>
       </c>
+      <c r="Z256" t="inlineStr"/>
+      <c r="AA256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -26414,6 +26934,8 @@
           <t>As Salam</t>
         </is>
       </c>
+      <c r="Z257" t="inlineStr"/>
+      <c r="AA257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -26515,6 +27037,8 @@
           <t>Al Khalidiyah</t>
         </is>
       </c>
+      <c r="Z258" t="inlineStr"/>
+      <c r="AA258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -26616,6 +27140,8 @@
           <t>As Safra</t>
         </is>
       </c>
+      <c r="Z259" t="inlineStr"/>
+      <c r="AA259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -26717,6 +27243,8 @@
           <t>Al Bishr</t>
         </is>
       </c>
+      <c r="Z260" t="inlineStr"/>
+      <c r="AA260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -26818,6 +27346,8 @@
           <t>Wahtan</t>
         </is>
       </c>
+      <c r="Z261" t="inlineStr"/>
+      <c r="AA261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -26919,6 +27449,8 @@
           <t>Al Mowata</t>
         </is>
       </c>
+      <c r="Z262" t="inlineStr"/>
+      <c r="AA262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -27020,6 +27552,8 @@
           <t>Al Rashid</t>
         </is>
       </c>
+      <c r="Z263" t="inlineStr"/>
+      <c r="AA263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -27121,6 +27655,8 @@
           <t>Al Hedaya</t>
         </is>
       </c>
+      <c r="Z264" t="inlineStr"/>
+      <c r="AA264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -27222,6 +27758,8 @@
           <t>Al Labidiyah</t>
         </is>
       </c>
+      <c r="Z265" t="inlineStr"/>
+      <c r="AA265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -27323,6 +27861,8 @@
           <t>Al Hedaya</t>
         </is>
       </c>
+      <c r="Z266" t="inlineStr"/>
+      <c r="AA266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -27424,6 +27964,8 @@
           <t>At Takhassusi</t>
         </is>
       </c>
+      <c r="Z267" t="inlineStr"/>
+      <c r="AA267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -27525,6 +28067,8 @@
           <t>An Nahdah</t>
         </is>
       </c>
+      <c r="Z268" t="inlineStr"/>
+      <c r="AA268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -27626,6 +28170,8 @@
           <t>Ibn Subayh</t>
         </is>
       </c>
+      <c r="Z269" t="inlineStr"/>
+      <c r="AA269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -27727,6 +28273,8 @@
           <t>As Sabihah</t>
         </is>
       </c>
+      <c r="Z270" t="inlineStr"/>
+      <c r="AA270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -27828,6 +28376,8 @@
           <t>As Sadah</t>
         </is>
       </c>
+      <c r="Z271" t="inlineStr"/>
+      <c r="AA271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -27929,6 +28479,8 @@
           <t>Al Awazim</t>
         </is>
       </c>
+      <c r="Z272" t="inlineStr"/>
+      <c r="AA272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -28030,6 +28582,8 @@
           <t>Al Hedaya</t>
         </is>
       </c>
+      <c r="Z273" t="inlineStr"/>
+      <c r="AA273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -28131,6 +28685,8 @@
           <t>Ain Adh Dhib</t>
         </is>
       </c>
+      <c r="Z274" t="inlineStr"/>
+      <c r="AA274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -28232,6 +28788,8 @@
           <t>Al Bishr</t>
         </is>
       </c>
+      <c r="Z275" t="inlineStr"/>
+      <c r="AA275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -28333,6 +28891,8 @@
           <t>Ibn Subayh</t>
         </is>
       </c>
+      <c r="Z276" t="inlineStr"/>
+      <c r="AA276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -28434,6 +28994,8 @@
           <t>Al Awazim</t>
         </is>
       </c>
+      <c r="Z277" t="inlineStr"/>
+      <c r="AA277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -28535,6 +29097,8 @@
           <t>Ghannamah</t>
         </is>
       </c>
+      <c r="Z278" t="inlineStr"/>
+      <c r="AA278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -28636,6 +29200,8 @@
           <t>Al Khalidiyah</t>
         </is>
       </c>
+      <c r="Z279" t="inlineStr"/>
+      <c r="AA279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -28737,6 +29303,8 @@
           <t>Qurtubah</t>
         </is>
       </c>
+      <c r="Z280" t="inlineStr"/>
+      <c r="AA280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -28838,6 +29406,8 @@
           <t>Qurtubah</t>
         </is>
       </c>
+      <c r="Z281" t="inlineStr"/>
+      <c r="AA281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -28939,6 +29509,8 @@
           <t>Al Buraykah</t>
         </is>
       </c>
+      <c r="Z282" t="inlineStr"/>
+      <c r="AA282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -29040,6 +29612,8 @@
           <t>At Takhassusi</t>
         </is>
       </c>
+      <c r="Z283" t="inlineStr"/>
+      <c r="AA283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -29141,6 +29715,8 @@
           <t>As Sadah</t>
         </is>
       </c>
+      <c r="Z284" t="inlineStr"/>
+      <c r="AA284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -29242,6 +29818,8 @@
           <t>As Salmiyah</t>
         </is>
       </c>
+      <c r="Z285" t="inlineStr"/>
+      <c r="AA285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -29343,6 +29921,8 @@
           <t>At Taghirah</t>
         </is>
       </c>
+      <c r="Z286" t="inlineStr"/>
+      <c r="AA286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -29444,6 +30024,8 @@
           <t>As Safra</t>
         </is>
       </c>
+      <c r="Z287" t="inlineStr"/>
+      <c r="AA287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -29545,6 +30127,8 @@
           <t>Al Hedaya</t>
         </is>
       </c>
+      <c r="Z288" t="inlineStr"/>
+      <c r="AA288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -29646,6 +30230,8 @@
           <t>Al Mowata</t>
         </is>
       </c>
+      <c r="Z289" t="inlineStr"/>
+      <c r="AA289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -29747,6 +30333,8 @@
           <t>As Salmiyah</t>
         </is>
       </c>
+      <c r="Z290" t="inlineStr"/>
+      <c r="AA290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -29848,6 +30436,8 @@
           <t>An Naqib</t>
         </is>
       </c>
+      <c r="Z291" t="inlineStr"/>
+      <c r="AA291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -29949,6 +30539,8 @@
           <t>As Salam</t>
         </is>
       </c>
+      <c r="Z292" t="inlineStr"/>
+      <c r="AA292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -30050,6 +30642,8 @@
           <t>Al Wasita</t>
         </is>
       </c>
+      <c r="Z293" t="inlineStr"/>
+      <c r="AA293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -30151,6 +30745,8 @@
           <t>An Naqib</t>
         </is>
       </c>
+      <c r="Z294" t="inlineStr"/>
+      <c r="AA294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -30252,6 +30848,8 @@
           <t>Al Amn</t>
         </is>
       </c>
+      <c r="Z295" t="inlineStr"/>
+      <c r="AA295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -30353,6 +30951,8 @@
           <t>Al Ajibah</t>
         </is>
       </c>
+      <c r="Z296" t="inlineStr"/>
+      <c r="AA296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -30454,6 +31054,8 @@
           <t>Al Mowata</t>
         </is>
       </c>
+      <c r="Z297" t="inlineStr"/>
+      <c r="AA297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -30555,6 +31157,8 @@
           <t>Al Ufuq</t>
         </is>
       </c>
+      <c r="Z298" t="inlineStr"/>
+      <c r="AA298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -30656,6 +31260,8 @@
           <t>An Naqib</t>
         </is>
       </c>
+      <c r="Z299" t="inlineStr"/>
+      <c r="AA299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -30757,6 +31363,8 @@
           <t>At Taghirah</t>
         </is>
       </c>
+      <c r="Z300" t="inlineStr"/>
+      <c r="AA300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -30858,6 +31466,8 @@
           <t>Al Khalidiyah</t>
         </is>
       </c>
+      <c r="Z301" t="inlineStr"/>
+      <c r="AA301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -30959,6 +31569,8 @@
           <t>Ghannamah</t>
         </is>
       </c>
+      <c r="Z302" t="inlineStr"/>
+      <c r="AA302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -31060,6 +31672,8 @@
           <t>Al Ufuq</t>
         </is>
       </c>
+      <c r="Z303" t="inlineStr"/>
+      <c r="AA303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -31161,6 +31775,8 @@
           <t>Mishal</t>
         </is>
       </c>
+      <c r="Z304" t="inlineStr"/>
+      <c r="AA304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -31262,6 +31878,8 @@
           <t>Al Amn</t>
         </is>
       </c>
+      <c r="Z305" t="inlineStr"/>
+      <c r="AA305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -31363,6 +31981,8 @@
           <t>Al Fakhriyah</t>
         </is>
       </c>
+      <c r="Z306" t="inlineStr"/>
+      <c r="AA306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -31464,6 +32084,8 @@
           <t>Al Ufuq</t>
         </is>
       </c>
+      <c r="Z307" t="inlineStr"/>
+      <c r="AA307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -31565,6 +32187,8 @@
           <t>Az Zirai</t>
         </is>
       </c>
+      <c r="Z308" t="inlineStr"/>
+      <c r="AA308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -31666,6 +32290,8 @@
           <t>Al Ulya</t>
         </is>
       </c>
+      <c r="Z309" t="inlineStr"/>
+      <c r="AA309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -31767,6 +32393,8 @@
           <t>Wahtan</t>
         </is>
       </c>
+      <c r="Z310" t="inlineStr"/>
+      <c r="AA310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -31868,6 +32496,8 @@
           <t>As Sadah</t>
         </is>
       </c>
+      <c r="Z311" t="inlineStr"/>
+      <c r="AA311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -31969,6 +32599,8 @@
           <t>Qurtubah</t>
         </is>
       </c>
+      <c r="Z312" t="inlineStr"/>
+      <c r="AA312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -32070,6 +32702,8 @@
           <t>An Naqa Ash Sharqi</t>
         </is>
       </c>
+      <c r="Z313" t="inlineStr"/>
+      <c r="AA313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -32171,6 +32805,8 @@
           <t>Al Hedaya</t>
         </is>
       </c>
+      <c r="Z314" t="inlineStr"/>
+      <c r="AA314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -32272,6 +32908,8 @@
           <t>Al Iskan</t>
         </is>
       </c>
+      <c r="Z315" t="inlineStr"/>
+      <c r="AA315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -32373,6 +33011,8 @@
           <t>At Taghirah</t>
         </is>
       </c>
+      <c r="Z316" t="inlineStr"/>
+      <c r="AA316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -32474,6 +33114,8 @@
           <t>Al Ulya</t>
         </is>
       </c>
+      <c r="Z317" t="inlineStr"/>
+      <c r="AA317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -32575,6 +33217,8 @@
           <t>Al Fakhriyah</t>
         </is>
       </c>
+      <c r="Z318" t="inlineStr"/>
+      <c r="AA318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -32676,6 +33320,8 @@
           <t>Al Labidiyah</t>
         </is>
       </c>
+      <c r="Z319" t="inlineStr"/>
+      <c r="AA319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -32777,6 +33423,8 @@
           <t>An Nasariyah</t>
         </is>
       </c>
+      <c r="Z320" t="inlineStr"/>
+      <c r="AA320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -32878,6 +33526,8 @@
           <t>Al Bishr</t>
         </is>
       </c>
+      <c r="Z321" t="inlineStr"/>
+      <c r="AA321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -32979,6 +33629,8 @@
           <t>Al Hedaya</t>
         </is>
       </c>
+      <c r="Z322" t="inlineStr"/>
+      <c r="AA322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -33080,6 +33732,8 @@
           <t>Al Hedaya</t>
         </is>
       </c>
+      <c r="Z323" t="inlineStr"/>
+      <c r="AA323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -33181,6 +33835,8 @@
           <t>Al Fakhriyah</t>
         </is>
       </c>
+      <c r="Z324" t="inlineStr"/>
+      <c r="AA324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -33282,6 +33938,8 @@
           <t>Al Mowata</t>
         </is>
       </c>
+      <c r="Z325" t="inlineStr"/>
+      <c r="AA325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -33383,6 +34041,8 @@
           <t>Al Muntazah</t>
         </is>
       </c>
+      <c r="Z326" t="inlineStr"/>
+      <c r="AA326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -33484,6 +34144,8 @@
           <t>Al Hedaya</t>
         </is>
       </c>
+      <c r="Z327" t="inlineStr"/>
+      <c r="AA327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -33585,6 +34247,8 @@
           <t>Jameana</t>
         </is>
       </c>
+      <c r="Z328" t="inlineStr"/>
+      <c r="AA328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -33686,6 +34350,8 @@
           <t>Al Ajibah</t>
         </is>
       </c>
+      <c r="Z329" t="inlineStr"/>
+      <c r="AA329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -33787,6 +34453,8 @@
           <t>As Safra</t>
         </is>
       </c>
+      <c r="Z330" t="inlineStr"/>
+      <c r="AA330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -33888,6 +34556,8 @@
           <t>Az Zirai</t>
         </is>
       </c>
+      <c r="Z331" t="inlineStr"/>
+      <c r="AA331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -33989,6 +34659,8 @@
           <t>As Salam</t>
         </is>
       </c>
+      <c r="Z332" t="inlineStr"/>
+      <c r="AA332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -34090,6 +34762,8 @@
           <t>Al Bishr</t>
         </is>
       </c>
+      <c r="Z333" t="inlineStr"/>
+      <c r="AA333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -34191,6 +34865,8 @@
           <t>Al Awazim</t>
         </is>
       </c>
+      <c r="Z334" t="inlineStr"/>
+      <c r="AA334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -34292,6 +34968,8 @@
           <t>Qurtubah</t>
         </is>
       </c>
+      <c r="Z335" t="inlineStr"/>
+      <c r="AA335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -34393,6 +35071,8 @@
           <t>Al Khalidiyah</t>
         </is>
       </c>
+      <c r="Z336" t="inlineStr"/>
+      <c r="AA336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -34494,6 +35174,8 @@
           <t>Al Awazim</t>
         </is>
       </c>
+      <c r="Z337" t="inlineStr"/>
+      <c r="AA337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -34595,6 +35277,8 @@
           <t>Al Khalidiyah</t>
         </is>
       </c>
+      <c r="Z338" t="inlineStr"/>
+      <c r="AA338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -34696,6 +35380,170 @@
           <t>Al Jamioyin</t>
         </is>
       </c>
+      <c r="Z339" t="inlineStr"/>
+      <c r="AA339" t="inlineStr"/>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>غير مطابق (Non-Compliant)</t>
+        </is>
+      </c>
+      <c r="B340" t="n">
+        <v>10</v>
+      </c>
+      <c r="C340" t="n">
+        <v>60</v>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>Bifenazate</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>شمام</t>
+        </is>
+      </c>
+      <c r="F340" s="2" t="n">
+        <v>45997</v>
+      </c>
+      <c r="G340" t="inlineStr"/>
+      <c r="H340" t="inlineStr"/>
+      <c r="I340" t="inlineStr"/>
+      <c r="J340" t="inlineStr"/>
+      <c r="K340" t="inlineStr"/>
+      <c r="L340" t="inlineStr"/>
+      <c r="M340" t="inlineStr"/>
+      <c r="N340" t="inlineStr"/>
+      <c r="O340" t="inlineStr"/>
+      <c r="P340" t="inlineStr"/>
+      <c r="Q340" t="n">
+        <v>0</v>
+      </c>
+      <c r="R340" t="n">
+        <v>6</v>
+      </c>
+      <c r="S340" t="inlineStr"/>
+      <c r="T340" t="inlineStr"/>
+      <c r="U340" t="inlineStr"/>
+      <c r="V340" t="inlineStr"/>
+      <c r="W340" t="inlineStr"/>
+      <c r="X340" t="inlineStr">
+        <is>
+          <t>الأفق</t>
+        </is>
+      </c>
+      <c r="Y340" t="inlineStr"/>
+      <c r="Z340" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA340" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>مطابق</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>100</v>
+      </c>
+      <c r="C341" t="n">
+        <v>50</v>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>Atrazine</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>باذنجان</t>
+        </is>
+      </c>
+      <c r="F341" s="2" t="n">
+        <v>45997</v>
+      </c>
+      <c r="G341" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H341" t="n">
+        <v>12</v>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="J341" t="n">
+        <v>49</v>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>manual_entry</t>
+        </is>
+      </c>
+      <c r="L341" t="n">
+        <v>2025</v>
+      </c>
+      <c r="M341" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="N341" t="inlineStr">
+        <is>
+          <t>Atrazine</t>
+        </is>
+      </c>
+      <c r="O341" t="inlineStr">
+        <is>
+          <t>herbicide</t>
+        </is>
+      </c>
+      <c r="P341" t="inlineStr">
+        <is>
+          <t>eggplant</t>
+        </is>
+      </c>
+      <c r="Q341" t="n">
+        <v>1</v>
+      </c>
+      <c r="R341" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S341" t="n">
+        <v>1</v>
+      </c>
+      <c r="T341" t="inlineStr">
+        <is>
+          <t>fruit_vegetables</t>
+        </is>
+      </c>
+      <c r="U341" t="n">
+        <v>3.931825632724326</v>
+      </c>
+      <c r="V341" t="n">
+        <v>4.61512051684126</v>
+      </c>
+      <c r="W341" t="n">
+        <v>0</v>
+      </c>
+      <c r="X341" t="inlineStr">
+        <is>
+          <t>ابن صبيح</t>
+        </is>
+      </c>
+      <c r="Y341" t="inlineStr">
+        <is>
+          <t>Ibn Subayh</t>
+        </is>
+      </c>
+      <c r="Z341" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA341" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
